--- a/assets/npv/Capital Budgeting Rules Review Solutions.xlsx
+++ b/assets/npv/Capital Budgeting Rules Review Solutions.xlsx
@@ -1,43 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox\Courses\Teaching\Financial Analytics\Course\4 - Capital Budgeting &amp; Project Financing\4 - Exercises\1 - Review\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox (Personal)\Courses\Teaching\Financial Analytics Spring 2025\Course\2 - Capital Budgeting\4 - Exercises\1 - Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9585B482-BCB6-42F5-BBBE-26E921013070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3487BF9-921A-4C05-B0DF-BD4B4FEC5287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10876" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10876" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Altenergy Soln Table" sheetId="2" state="hidden" r:id="rId1"/>
-    <sheet name="Domino's" sheetId="16" r:id="rId2"/>
-    <sheet name="Regression" sheetId="22" r:id="rId3"/>
-    <sheet name="WACC" sheetId="20" r:id="rId4"/>
-    <sheet name="Investment Rules" sheetId="1" r:id="rId5"/>
+    <sheet name="Investment Rules" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="beta_a">WACC!$B$6</definedName>
-    <definedName name="beta_dom">Regression!$B$18</definedName>
-    <definedName name="beta_e">WACC!$B$8</definedName>
-    <definedName name="de">WACC!$B$7</definedName>
-    <definedName name="de_dom">WACC!$B$3</definedName>
-    <definedName name="debt_weight">WACC!$B$17</definedName>
-    <definedName name="ds">WACC!$B$14</definedName>
-    <definedName name="equity_weight">WACC!$B$18</definedName>
+    <definedName name="cost_capital">'Investment Rules'!$H$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Altenergy Soln Table'!$A$1:$I$48</definedName>
-    <definedName name="r_d">WACC!$B$15</definedName>
-    <definedName name="r_e">WACC!$B$11</definedName>
-    <definedName name="rf_20">WACC!$B$13</definedName>
-    <definedName name="rf_30">WACC!$B$9</definedName>
-    <definedName name="rp_m">WACC!$B$10</definedName>
-    <definedName name="tax">WACC!$B$4</definedName>
-    <definedName name="wacc">WACC!$B$19</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -55,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
   <si>
     <t>Devices sold</t>
   </si>
@@ -486,126 +469,6 @@
     <t>NPV</t>
   </si>
   <si>
-    <t>Tax Rate</t>
-  </si>
-  <si>
-    <t>Cost of Debt</t>
-  </si>
-  <si>
-    <t>WACC</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Domino's Excess Return</t>
-  </si>
-  <si>
-    <t>Market Excess Return</t>
-  </si>
-  <si>
-    <t>SUMMARY OUTPUT</t>
-  </si>
-  <si>
-    <t>Regression Statistics</t>
-  </si>
-  <si>
-    <t>Multiple R</t>
-  </si>
-  <si>
-    <t>R Square</t>
-  </si>
-  <si>
-    <t>Adjusted R Square</t>
-  </si>
-  <si>
-    <t>Standard Error</t>
-  </si>
-  <si>
-    <t>Observations</t>
-  </si>
-  <si>
-    <t>ANOVA</t>
-  </si>
-  <si>
-    <t>Regression</t>
-  </si>
-  <si>
-    <t>Residual</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Intercept</t>
-  </si>
-  <si>
-    <t>df</t>
-  </si>
-  <si>
-    <t>SS</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Significance F</t>
-  </si>
-  <si>
-    <t>Coefficients</t>
-  </si>
-  <si>
-    <t>t Stat</t>
-  </si>
-  <si>
-    <t>P-value</t>
-  </si>
-  <si>
-    <t>Lower 95%</t>
-  </si>
-  <si>
-    <t>Upper 95%</t>
-  </si>
-  <si>
-    <t>Domino's Equity beta</t>
-  </si>
-  <si>
-    <t>Domino's D/E</t>
-  </si>
-  <si>
-    <t>Asset beta</t>
-  </si>
-  <si>
-    <t>D/E</t>
-  </si>
-  <si>
-    <t>Equity beta</t>
-  </si>
-  <si>
-    <t>30-yr Rf</t>
-  </si>
-  <si>
-    <t>Market Risk Premium</t>
-  </si>
-  <si>
-    <t>20-yr Rf</t>
-  </si>
-  <si>
-    <t>Default Spread</t>
-  </si>
-  <si>
-    <t>Cost of Equity</t>
-  </si>
-  <si>
-    <t>Debt Weight</t>
-  </si>
-  <si>
-    <t>Equity Weight</t>
-  </si>
-  <si>
     <t>Projected Cash Flows</t>
   </si>
   <si>
@@ -616,23 +479,24 @@
   </si>
   <si>
     <t>Hurdle Rate</t>
+  </si>
+  <si>
+    <t>Cost of Capital r</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+  <numFmts count="6">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="173" formatCode="mm/yyyy"/>
-    <numFmt numFmtId="177" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -720,14 +584,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -738,14 +594,6 @@
       <color indexed="8"/>
       <name val="Times New Roman"/>
       <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -767,7 +615,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -900,17 +748,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -920,10 +757,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -953,11 +790,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -974,10 +811,10 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -989,7 +826,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1000,7 +837,20 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1010,59 +860,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="177" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2142,32 +1940,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:G47"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="20.796875" customWidth="1"/>
+    <col min="1" max="1" width="20.86328125" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="3" max="3" width="13.06640625" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" customWidth="1"/>
-    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.06640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" customWidth="1"/>
+    <col min="7" max="7" width="14.3984375" customWidth="1"/>
     <col min="8" max="8" width="10.73046875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="32.33203125" customWidth="1"/>
-    <col min="12" max="12" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="32.265625" customWidth="1"/>
+    <col min="12" max="12" width="13.86328125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="72.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
     </row>
     <row r="2" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2"/>
@@ -2215,7 +2013,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="51" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="8"/>
@@ -2236,7 +2034,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A7" s="43"/>
+      <c r="A7" s="52"/>
       <c r="B7" s="11"/>
       <c r="C7" s="12" t="s">
         <v>10</v>
@@ -2321,15 +2119,15 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="83.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
@@ -2356,15 +2154,15 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="41" t="s">
+      <c r="A18" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
+      <c r="B18" s="50"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="5" t="s">
@@ -2396,7 +2194,7 @@
       </c>
     </row>
     <row r="20" spans="1:7" s="22" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="42" t="s">
+      <c r="A20" s="51" t="s">
         <v>18</v>
       </c>
       <c r="B20" s="8"/>
@@ -2419,7 +2217,7 @@
       </c>
     </row>
     <row r="21" spans="1:7" s="22" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="43"/>
+      <c r="A21" s="52"/>
       <c r="B21" s="11"/>
       <c r="C21" s="12" t="s">
         <v>19</v>
@@ -2644,15 +2442,15 @@
       </c>
     </row>
     <row r="32" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="41" t="s">
+      <c r="A32" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="41"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="41"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="50"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
@@ -2968,1154 +2766,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE79D4E9-2D7A-477A-8F14-374CF07FB56D}">
-  <dimension ref="A1:D61"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="7.46484375" style="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.265625" style="48" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.3984375" style="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.06640625" style="44"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="46" t="s">
-        <v>43</v>
-      </c>
-      <c r="C1" s="46" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" s="47">
-        <v>43556</v>
-      </c>
-      <c r="B2" s="48">
-        <v>4.6938179427091983E-2</v>
-      </c>
-      <c r="C2" s="48">
-        <v>3.9699999999999999E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" s="47">
-        <v>43586</v>
-      </c>
-      <c r="B3" s="48">
-        <v>2.87661814937352E-2</v>
-      </c>
-      <c r="C3" s="48">
-        <v>-6.9400000000000003E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" s="47">
-        <v>43617</v>
-      </c>
-      <c r="B4" s="48">
-        <v>-7.9647393336981856E-3</v>
-      </c>
-      <c r="C4" s="48">
-        <v>6.93E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" s="47">
-        <v>43647</v>
-      </c>
-      <c r="B5" s="48">
-        <v>-0.12305085645039024</v>
-      </c>
-      <c r="C5" s="48">
-        <v>1.1899999999999999E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" s="47">
-        <v>43678</v>
-      </c>
-      <c r="B6" s="48">
-        <v>-7.5542986096155423E-2</v>
-      </c>
-      <c r="C6" s="48">
-        <v>-2.58E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" s="47">
-        <v>43709</v>
-      </c>
-      <c r="B7" s="48">
-        <v>7.4649089658348544E-2</v>
-      </c>
-      <c r="C7" s="48">
-        <v>1.43E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" s="47">
-        <v>43739</v>
-      </c>
-      <c r="B8" s="48">
-        <v>0.1102169428263525</v>
-      </c>
-      <c r="C8" s="48">
-        <v>2.06E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" s="47">
-        <v>43770</v>
-      </c>
-      <c r="B9" s="48">
-        <v>8.1098880249745375E-2</v>
-      </c>
-      <c r="C9" s="48">
-        <v>3.8699999999999998E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A10" s="47">
-        <v>43800</v>
-      </c>
-      <c r="B10" s="48">
-        <v>-4.56683869885963E-3</v>
-      </c>
-      <c r="C10" s="48">
-        <v>2.7699999999999999E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A11" s="47">
-        <v>43831</v>
-      </c>
-      <c r="B11" s="48">
-        <v>-4.1421200089901869E-2</v>
-      </c>
-      <c r="C11" s="48">
-        <v>-1.1000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A12" s="47">
-        <v>43862</v>
-      </c>
-      <c r="B12" s="48">
-        <v>0.20242688352126209</v>
-      </c>
-      <c r="C12" s="48">
-        <v>-8.1300000000000011E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A13" s="47">
-        <v>43891</v>
-      </c>
-      <c r="B13" s="48">
-        <v>-4.7936649936314926E-2</v>
-      </c>
-      <c r="C13" s="48">
-        <v>-0.13390000000000002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A14" s="47">
-        <v>43922</v>
-      </c>
-      <c r="B14" s="48">
-        <v>0.11945140330557691</v>
-      </c>
-      <c r="C14" s="48">
-        <v>0.13650000000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A15" s="47">
-        <v>43952</v>
-      </c>
-      <c r="B15" s="48">
-        <v>6.5862594448764494E-2</v>
-      </c>
-      <c r="C15" s="48">
-        <v>5.5800000000000002E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A16" s="47">
-        <v>43983</v>
-      </c>
-      <c r="B16" s="48">
-        <v>-4.270470620423597E-2</v>
-      </c>
-      <c r="C16" s="48">
-        <v>2.46E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A17" s="47">
-        <v>44013</v>
-      </c>
-      <c r="B17" s="48">
-        <v>4.8412492868254303E-2</v>
-      </c>
-      <c r="C17" s="48">
-        <v>5.7699999999999994E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A18" s="47">
-        <v>44044</v>
-      </c>
-      <c r="B18" s="48">
-        <v>5.7610055152415435E-2</v>
-      </c>
-      <c r="C18" s="48">
-        <v>7.6299999999999993E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A19" s="47">
-        <v>44075</v>
-      </c>
-      <c r="B19" s="48">
-        <v>3.9706146694331562E-2</v>
-      </c>
-      <c r="C19" s="48">
-        <v>-3.6299999999999999E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A20" s="47">
-        <v>44105</v>
-      </c>
-      <c r="B20" s="48">
-        <v>-0.1088595984399561</v>
-      </c>
-      <c r="C20" s="48">
-        <v>-2.1000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A21" s="47">
-        <v>44136</v>
-      </c>
-      <c r="B21" s="48">
-        <v>3.7466143299758919E-2</v>
-      </c>
-      <c r="C21" s="48">
-        <v>0.12470000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A22" s="47">
-        <v>44166</v>
-      </c>
-      <c r="B22" s="48">
-        <v>-2.3405811466215808E-2</v>
-      </c>
-      <c r="C22" s="48">
-        <v>4.6300000000000001E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A23" s="47">
-        <v>44197</v>
-      </c>
-      <c r="B23" s="48">
-        <v>-3.1348282290697214E-2</v>
-      </c>
-      <c r="C23" s="48">
-        <v>-2.9999999999999997E-4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A24" s="47">
-        <v>44228</v>
-      </c>
-      <c r="B24" s="48">
-        <v>-6.5405929618498559E-2</v>
-      </c>
-      <c r="C24" s="48">
-        <v>2.7799999999999998E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A25" s="47">
-        <v>44256</v>
-      </c>
-      <c r="B25" s="48">
-        <v>6.1411870388508039E-2</v>
-      </c>
-      <c r="C25" s="48">
-        <v>3.0800000000000001E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A26" s="47">
-        <v>44287</v>
-      </c>
-      <c r="B26" s="48">
-        <v>0.15133843875944608</v>
-      </c>
-      <c r="C26" s="48">
-        <v>4.9299999999999997E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A27" s="47">
-        <v>44317</v>
-      </c>
-      <c r="B27" s="48">
-        <v>1.0725910875815092E-2</v>
-      </c>
-      <c r="C27" s="48">
-        <v>2.8999999999999998E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A28" s="47">
-        <v>44348</v>
-      </c>
-      <c r="B28" s="48">
-        <v>9.2815167973135049E-2</v>
-      </c>
-      <c r="C28" s="48">
-        <v>2.75E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A29" s="47">
-        <v>44378</v>
-      </c>
-      <c r="B29" s="48">
-        <v>0.12881914328632038</v>
-      </c>
-      <c r="C29" s="48">
-        <v>1.2699999999999999E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A30" s="47">
-        <v>44409</v>
-      </c>
-      <c r="B30" s="48">
-        <v>-1.6365684056155572E-2</v>
-      </c>
-      <c r="C30" s="48">
-        <v>2.9100000000000001E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A31" s="47">
-        <v>44440</v>
-      </c>
-      <c r="B31" s="48">
-        <v>-7.7250533518401387E-2</v>
-      </c>
-      <c r="C31" s="48">
-        <v>-4.3700000000000003E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A32" s="47">
-        <v>44470</v>
-      </c>
-      <c r="B32" s="48">
-        <v>2.7069305437598334E-2</v>
-      </c>
-      <c r="C32" s="48">
-        <v>6.6500000000000004E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A33" s="47">
-        <v>44501</v>
-      </c>
-      <c r="B33" s="48">
-        <v>7.1926692586098628E-2</v>
-      </c>
-      <c r="C33" s="48">
-        <v>-1.55E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A34" s="47">
-        <v>44531</v>
-      </c>
-      <c r="B34" s="48">
-        <v>7.6477876125703198E-2</v>
-      </c>
-      <c r="C34" s="48">
-        <v>3.1E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A35" s="47">
-        <v>44562</v>
-      </c>
-      <c r="B35" s="48">
-        <v>-0.19294267542349486</v>
-      </c>
-      <c r="C35" s="48">
-        <v>-6.25E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A36" s="47">
-        <v>44593</v>
-      </c>
-      <c r="B36" s="48">
-        <v>-4.9356493875062357E-2</v>
-      </c>
-      <c r="C36" s="48">
-        <v>-2.29E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A37" s="47">
-        <v>44621</v>
-      </c>
-      <c r="B37" s="48">
-        <v>-5.8504992015434826E-2</v>
-      </c>
-      <c r="C37" s="48">
-        <v>3.0499999999999999E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A38" s="47">
-        <v>44652</v>
-      </c>
-      <c r="B38" s="48">
-        <v>-0.16738256979733035</v>
-      </c>
-      <c r="C38" s="48">
-        <v>-9.4600000000000004E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A39" s="47">
-        <v>44682</v>
-      </c>
-      <c r="B39" s="48">
-        <v>7.3867501552724313E-2</v>
-      </c>
-      <c r="C39" s="48">
-        <v>-3.4000000000000002E-3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A40" s="47">
-        <v>44713</v>
-      </c>
-      <c r="B40" s="48">
-        <v>7.1878594912704846E-2</v>
-      </c>
-      <c r="C40" s="48">
-        <v>-8.43E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A41" s="47">
-        <v>44743</v>
-      </c>
-      <c r="B41" s="48">
-        <v>7.4746373192076561E-3</v>
-      </c>
-      <c r="C41" s="48">
-        <v>9.5700000000000007E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A42" s="47">
-        <v>44774</v>
-      </c>
-      <c r="B42" s="48">
-        <v>-5.5443693447610104E-2</v>
-      </c>
-      <c r="C42" s="48">
-        <v>-3.7699999999999997E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A43" s="47">
-        <v>44805</v>
-      </c>
-      <c r="B43" s="48">
-        <v>-0.1696148885336074</v>
-      </c>
-      <c r="C43" s="48">
-        <v>-9.35E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A44" s="47">
-        <v>44835</v>
-      </c>
-      <c r="B44" s="48">
-        <v>6.982369871498445E-2</v>
-      </c>
-      <c r="C44" s="48">
-        <v>7.8299999999999995E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A45" s="47">
-        <v>44866</v>
-      </c>
-      <c r="B45" s="48">
-        <v>0.16422779737179183</v>
-      </c>
-      <c r="C45" s="48">
-        <v>4.5999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A46" s="47">
-        <v>44896</v>
-      </c>
-      <c r="B46" s="48">
-        <v>-0.11549307395112535</v>
-      </c>
-      <c r="C46" s="48">
-        <v>-6.4100000000000004E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A47" s="47">
-        <v>44927</v>
-      </c>
-      <c r="B47" s="48">
-        <v>1.5160287821442416E-2</v>
-      </c>
-      <c r="C47" s="48">
-        <v>6.6500000000000004E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A48" s="47">
-        <v>44958</v>
-      </c>
-      <c r="B48" s="48">
-        <v>-0.17391046816265099</v>
-      </c>
-      <c r="C48" s="48">
-        <v>-2.58E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A49" s="47">
-        <v>44986</v>
-      </c>
-      <c r="B49" s="48">
-        <v>0.11476872556147141</v>
-      </c>
-      <c r="C49" s="48">
-        <v>2.5099999999999997E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A50" s="47">
-        <v>45017</v>
-      </c>
-      <c r="B50" s="48">
-        <v>-4.0726692863743863E-2</v>
-      </c>
-      <c r="C50" s="48">
-        <v>6.0999999999999995E-3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A51" s="47">
-        <v>45047</v>
-      </c>
-      <c r="B51" s="48">
-        <v>-9.4200350887873735E-2</v>
-      </c>
-      <c r="C51" s="48">
-        <v>3.4999999999999996E-3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A52" s="47">
-        <v>45078</v>
-      </c>
-      <c r="B52" s="48">
-        <v>0.15463590909412006</v>
-      </c>
-      <c r="C52" s="48">
-        <v>6.4600000000000005E-2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A53" s="47">
-        <v>45108</v>
-      </c>
-      <c r="B53" s="48">
-        <v>0.1730425258368159</v>
-      </c>
-      <c r="C53" s="48">
-        <v>3.2099999999999997E-2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A54" s="47">
-        <v>45139</v>
-      </c>
-      <c r="B54" s="48">
-        <v>-3.2541829623674572E-2</v>
-      </c>
-      <c r="C54" s="48">
-        <v>-2.3900000000000001E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A55" s="47">
-        <v>45170</v>
-      </c>
-      <c r="B55" s="48">
-        <v>-3.0825054122765649E-2</v>
-      </c>
-      <c r="C55" s="48">
-        <v>-5.2400000000000002E-2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A56" s="47">
-        <v>45200</v>
-      </c>
-      <c r="B56" s="48">
-        <v>-0.11173176326148096</v>
-      </c>
-      <c r="C56" s="48">
-        <v>-3.1899999999999998E-2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A57" s="47">
-        <v>45231</v>
-      </c>
-      <c r="B57" s="48">
-        <v>0.15020177790044426</v>
-      </c>
-      <c r="C57" s="48">
-        <v>8.8399999999999992E-2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A58" s="47">
-        <v>45261</v>
-      </c>
-      <c r="B58" s="48">
-        <v>4.0625018324663642E-2</v>
-      </c>
-      <c r="C58" s="48">
-        <v>4.8499999999999995E-2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A59" s="47"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A60" s="47"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A61" s="47"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAEE092A-7DA7-41E0-A41C-767BDB6DE66A}">
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="17.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="12.59765625" style="34" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-    </row>
-    <row r="2" spans="1:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="49"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A3" s="55" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="55"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="50" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="56">
-        <v>0.47632527717454209</v>
-      </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="50" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="56">
-        <v>0.22688576967540436</v>
-      </c>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" s="50" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="56">
-        <v>0.21282914730586627</v>
-      </c>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A7" s="50" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="56">
-        <v>8.4584857374801828E-2</v>
-      </c>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-    </row>
-    <row r="8" spans="1:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="51" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="57">
-        <v>57</v>
-      </c>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="49"/>
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-    </row>
-    <row r="10" spans="1:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A11" s="52"/>
-      <c r="B11" s="52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="52" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="52" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11" s="53"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A12" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="56">
-        <v>1</v>
-      </c>
-      <c r="C12" s="56">
-        <v>0.11548126237637479</v>
-      </c>
-      <c r="D12" s="56">
-        <v>0.11548126237637479</v>
-      </c>
-      <c r="E12" s="56">
-        <v>16.140845482701813</v>
-      </c>
-      <c r="F12" s="56">
-        <v>1.8013275481093343E-4</v>
-      </c>
-      <c r="G12" s="53"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="50" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="56">
-        <v>55</v>
-      </c>
-      <c r="C13" s="56">
-        <v>0.39350289534135618</v>
-      </c>
-      <c r="D13" s="56">
-        <v>7.1545980971155672E-3</v>
-      </c>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="53"/>
-    </row>
-    <row r="14" spans="1:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" s="57">
-        <v>56</v>
-      </c>
-      <c r="C14" s="57">
-        <v>0.50898415771773098</v>
-      </c>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="53"/>
-    </row>
-    <row r="15" spans="1:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="49"/>
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A16" s="52"/>
-      <c r="B16" s="52" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="52" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="52" t="s">
-        <v>63</v>
-      </c>
-      <c r="E16" s="52" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" s="52" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16" s="52" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A17" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="56">
-        <v>2.4536838195976275E-3</v>
-      </c>
-      <c r="C17" s="56">
-        <v>1.139039989033953E-2</v>
-      </c>
-      <c r="D17" s="56">
-        <v>0.21541682848893262</v>
-      </c>
-      <c r="E17" s="56">
-        <v>0.83023920035922627</v>
-      </c>
-      <c r="F17" s="56">
-        <v>-2.0373187660214565E-2</v>
-      </c>
-      <c r="G17" s="56">
-        <v>2.528055529940982E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="51" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="58">
-        <v>0.80890069263577857</v>
-      </c>
-      <c r="C18" s="57">
-        <v>0.20134092860296079</v>
-      </c>
-      <c r="D18" s="57">
-        <v>4.0175671099188692</v>
-      </c>
-      <c r="E18" s="57">
-        <v>1.8013275481093031E-4</v>
-      </c>
-      <c r="F18" s="57">
-        <v>0.40540445500642269</v>
-      </c>
-      <c r="G18" s="57">
-        <v>1.2123969302651345</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A19" s="49"/>
-      <c r="B19" s="53"/>
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="53"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A20" s="49"/>
-      <c r="B20" s="53"/>
-      <c r="C20" s="53"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A21" s="49"/>
-      <c r="B21" s="53"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A3:B3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E92F460-40CC-4999-9390-CD28EDEC25AB}">
-  <dimension ref="A2:C19"/>
-  <sheetFormatPr defaultColWidth="6.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="17.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.73046875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B2" s="49">
-        <f>beta_dom</f>
-        <v>0.80890069263577857</v>
-      </c>
-      <c r="C2" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B2)</f>
-        <v>=beta_dom</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B3" s="59">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B6" s="49">
-        <f>beta_dom/(1+de_dom*(1-tax))</f>
-        <v>0.55152319952439455</v>
-      </c>
-      <c r="C6" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B6)</f>
-        <v>=beta_dom/(1+de_dom*(1-tax))</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B8" s="49">
-        <f>beta_a*(1+de*(1-tax))</f>
-        <v>0.93758943919147075</v>
-      </c>
-      <c r="C8" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B8)</f>
-        <v>=beta_a*(1+de*(1-tax))</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" s="1">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="1">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B11" s="61">
-        <f>rf_30+beta_e*rp_m</f>
-        <v>8.6255366351488241E-2</v>
-      </c>
-      <c r="C11" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B11)</f>
-        <v>=rf_30+beta_e*rp_m</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" s="60">
-        <v>2.75E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="1">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="60">
-        <f>rf_20+ds</f>
-        <v>5.7499999999999996E-2</v>
-      </c>
-      <c r="C15" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B15)</f>
-        <v>=rf_20+ds</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>78</v>
-      </c>
-      <c r="B18" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="61">
-        <f>debt_weight*r_d*(1-tax)+equity_weight*r_e</f>
-        <v>6.3252683175744118E-2</v>
-      </c>
-      <c r="C19" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(B19)</f>
-        <v>=debt_weight*r_d*(1-tax)+equity_weight*r_e</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5" style="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.59765625" style="34" customWidth="1"/>
-    <col min="3" max="3" width="12.59765625" customWidth="1"/>
-    <col min="4" max="4" width="8.796875" customWidth="1"/>
-    <col min="7" max="7" width="14.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" style="34" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="8.73046875" customWidth="1"/>
+    <col min="7" max="7" width="15.06640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="34.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4123,11 +2784,11 @@
       <c r="A1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="65" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="70" t="s">
-        <v>80</v>
+      <c r="B1" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="49" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="37" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
@@ -4137,7 +2798,7 @@
       <c r="B2" s="40">
         <v>-10000</v>
       </c>
-      <c r="C2" s="62">
+      <c r="C2" s="41">
         <f>B2</f>
         <v>-10000</v>
       </c>
@@ -4146,10 +2807,10 @@
         <v>=B2</v>
       </c>
       <c r="G2" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="H2" s="66">
-        <v>4</v>
+        <v>43</v>
+      </c>
+      <c r="H2" s="53">
+        <v>6.3299999999999995E-2</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
@@ -4159,7 +2820,7 @@
       <c r="B3" s="40">
         <v>-2000</v>
       </c>
-      <c r="C3" s="63">
+      <c r="C3" s="42">
         <f>B3+C2</f>
         <v>-12000</v>
       </c>
@@ -4167,17 +2828,6 @@
         <f ca="1">_xlfn.FORMULATEXT(C3)</f>
         <v>=B3+C2</v>
       </c>
-      <c r="G3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="67">
-        <f>IRR(B2:B22)</f>
-        <v>0.29082691091351531</v>
-      </c>
-      <c r="I3" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(H3)</f>
-        <v>=IRR(B2:B22)</v>
-      </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A4" s="39">
@@ -4186,20 +2836,9 @@
       <c r="B4" s="40">
         <v>3000</v>
       </c>
-      <c r="C4" s="63">
+      <c r="C4" s="42">
         <f t="shared" ref="C4:C22" si="0">B4+C3</f>
         <v>-9000</v>
-      </c>
-      <c r="G4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H4" s="68">
-        <f>wacc+25%</f>
-        <v>0.31325268317574412</v>
-      </c>
-      <c r="I4" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(H4)</f>
-        <v>=wacc+25%</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
@@ -4209,21 +2848,17 @@
       <c r="B5" s="40">
         <v>4000</v>
       </c>
-      <c r="C5" s="63">
+      <c r="C5" s="42">
         <f t="shared" si="0"/>
         <v>-5000</v>
       </c>
-      <c r="G5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="69">
-        <f>B2+NPV(wacc,'Investment Rules'!B3:B22)</f>
-        <v>36680.847226650971</v>
-      </c>
-      <c r="I5" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(H5)</f>
-        <v>=B2+NPV(wacc,'Investment Rules'!B3:B22)</v>
-      </c>
+      <c r="G5" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="45">
+        <v>4</v>
+      </c>
+      <c r="I5" s="37"/>
     </row>
     <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A6" s="39">
@@ -4232,9 +2867,20 @@
       <c r="B6" s="40">
         <v>5000</v>
       </c>
-      <c r="C6" s="64">
+      <c r="C6" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="46">
+        <f>IRR(B2:B22)</f>
+        <v>0.29082691091351531</v>
+      </c>
+      <c r="I6" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(H6)</f>
+        <v>=IRR(B2:B22)</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
@@ -4244,9 +2890,20 @@
       <c r="B7" s="40">
         <v>5000</v>
       </c>
-      <c r="C7" s="63">
+      <c r="C7" s="42">
         <f t="shared" si="0"/>
         <v>5000</v>
+      </c>
+      <c r="G7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="47">
+        <f>cost_capital+25%</f>
+        <v>0.31330000000000002</v>
+      </c>
+      <c r="I7" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(H7)</f>
+        <v>=cost_capital+25%</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
@@ -4256,9 +2913,20 @@
       <c r="B8" s="40">
         <v>5000</v>
       </c>
-      <c r="C8" s="63">
+      <c r="C8" s="42">
         <f t="shared" si="0"/>
         <v>10000</v>
+      </c>
+      <c r="G8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="48">
+        <f>B2+NPV(cost_capital,'Investment Rules'!B3:B22)</f>
+        <v>36660.257520786203</v>
+      </c>
+      <c r="I8" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(H8)</f>
+        <v>=B2+NPV(cost_capital,'Investment Rules'!B3:B22)</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
@@ -4268,7 +2936,7 @@
       <c r="B9" s="40">
         <v>5000</v>
       </c>
-      <c r="C9" s="63">
+      <c r="C9" s="42">
         <f t="shared" si="0"/>
         <v>15000</v>
       </c>
@@ -4280,7 +2948,7 @@
       <c r="B10" s="40">
         <v>5000</v>
       </c>
-      <c r="C10" s="63">
+      <c r="C10" s="42">
         <f t="shared" si="0"/>
         <v>20000</v>
       </c>
@@ -4292,7 +2960,7 @@
       <c r="B11" s="40">
         <v>5000</v>
       </c>
-      <c r="C11" s="63">
+      <c r="C11" s="42">
         <f t="shared" si="0"/>
         <v>25000</v>
       </c>
@@ -4304,7 +2972,7 @@
       <c r="B12" s="40">
         <v>5000</v>
       </c>
-      <c r="C12" s="63">
+      <c r="C12" s="42">
         <f t="shared" si="0"/>
         <v>30000</v>
       </c>
@@ -4316,7 +2984,7 @@
       <c r="B13" s="40">
         <v>5000</v>
       </c>
-      <c r="C13" s="63">
+      <c r="C13" s="42">
         <f t="shared" si="0"/>
         <v>35000</v>
       </c>
@@ -4328,7 +2996,7 @@
       <c r="B14" s="40">
         <v>5000</v>
       </c>
-      <c r="C14" s="63">
+      <c r="C14" s="42">
         <f t="shared" si="0"/>
         <v>40000</v>
       </c>
@@ -4340,7 +3008,7 @@
       <c r="B15" s="40">
         <v>5000</v>
       </c>
-      <c r="C15" s="63">
+      <c r="C15" s="42">
         <f t="shared" si="0"/>
         <v>45000</v>
       </c>
@@ -4352,7 +3020,7 @@
       <c r="B16" s="40">
         <v>5000</v>
       </c>
-      <c r="C16" s="63">
+      <c r="C16" s="42">
         <f t="shared" si="0"/>
         <v>50000</v>
       </c>
@@ -4364,7 +3032,7 @@
       <c r="B17" s="40">
         <v>5000</v>
       </c>
-      <c r="C17" s="63">
+      <c r="C17" s="42">
         <f t="shared" si="0"/>
         <v>55000</v>
       </c>
@@ -4376,7 +3044,7 @@
       <c r="B18" s="40">
         <v>5000</v>
       </c>
-      <c r="C18" s="63">
+      <c r="C18" s="42">
         <f t="shared" si="0"/>
         <v>60000</v>
       </c>
@@ -4388,7 +3056,7 @@
       <c r="B19" s="40">
         <v>5000</v>
       </c>
-      <c r="C19" s="63">
+      <c r="C19" s="42">
         <f t="shared" si="0"/>
         <v>65000</v>
       </c>
@@ -4400,7 +3068,7 @@
       <c r="B20" s="40">
         <v>5000</v>
       </c>
-      <c r="C20" s="63">
+      <c r="C20" s="42">
         <f t="shared" si="0"/>
         <v>70000</v>
       </c>
@@ -4412,7 +3080,7 @@
       <c r="B21" s="40">
         <v>5000</v>
       </c>
-      <c r="C21" s="63">
+      <c r="C21" s="42">
         <f t="shared" si="0"/>
         <v>75000</v>
       </c>
@@ -4424,7 +3092,7 @@
       <c r="B22" s="40">
         <v>5000</v>
       </c>
-      <c r="C22" s="63">
+      <c r="C22" s="42">
         <f t="shared" si="0"/>
         <v>80000</v>
       </c>
